--- a/GUA/IPPU/B1_Default_Param.xlsx
+++ b/GUA/IPPU/B1_Default_Param.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juanc\Desktop\GUA_Modelos_Sectoriales\M0_IPPU\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IgnacioAlfaroCorrale\Desktop\Models_running\IPPU_CR_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14F9ABF2-4D45-4E62-A0F7-82A21095F0D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDBB4A73-A45D-4874-86B7-0AC6BF8320C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{3D89E3D1-8F1A-4219-BF0E-B7FA6DD47AE2}"/>
+    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{3D89E3D1-8F1A-4219-BF0E-B7FA6DD47AE2}"/>
   </bookViews>
   <sheets>
     <sheet name="Default_Values" sheetId="1" r:id="rId1"/>
@@ -216,18 +216,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -242,10 +236,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -264,9 +257,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -304,7 +297,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -410,7 +403,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -552,7 +545,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -561,13 +554,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC90BEE7-74F3-4D80-B77F-CF05A093532F}">
   <dimension ref="A1:B53"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="40.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="40.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -575,7 +568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -583,15 +576,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3">
-        <v>99999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+        <v>9999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -599,7 +592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -607,7 +600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -615,7 +608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -623,7 +616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -631,7 +624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -639,7 +632,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -647,7 +640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -655,7 +648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -663,7 +656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -671,7 +664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -679,7 +672,7 @@
         <v>1.3699999999999999E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -687,7 +680,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -695,15 +688,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="2">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B17">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -711,7 +704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -719,7 +712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -727,7 +720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -735,7 +728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -743,15 +736,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>23</v>
       </c>
       <c r="B23">
-        <v>99999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+        <v>9999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -759,7 +752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -767,7 +760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>26</v>
       </c>
@@ -775,7 +768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -783,7 +776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>28</v>
       </c>
@@ -791,7 +784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>29</v>
       </c>
@@ -799,7 +792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>30</v>
       </c>
@@ -807,7 +800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>31</v>
       </c>
@@ -815,7 +808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>32</v>
       </c>
@@ -823,7 +816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>33</v>
       </c>
@@ -831,7 +824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>34</v>
       </c>
@@ -839,7 +832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>35</v>
       </c>
@@ -847,7 +840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>36</v>
       </c>
@@ -855,7 +848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>37</v>
       </c>
@@ -863,7 +856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>38</v>
       </c>
@@ -871,7 +864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>39</v>
       </c>
@@ -879,7 +872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>40</v>
       </c>
@@ -887,7 +880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>41</v>
       </c>
@@ -895,7 +888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>42</v>
       </c>
@@ -903,23 +896,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>43</v>
       </c>
       <c r="B43">
-        <v>99999</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+        <v>9999999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>44</v>
       </c>
       <c r="B44">
-        <v>99999</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+        <v>9999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>45</v>
       </c>
@@ -927,7 +920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>46</v>
       </c>
@@ -935,7 +928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>47</v>
       </c>
@@ -943,15 +936,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>48</v>
       </c>
       <c r="B48">
-        <v>99999</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+        <v>9999999999</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>49</v>
       </c>
@@ -959,15 +952,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>50</v>
       </c>
       <c r="B50">
-        <v>99999</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+        <v>9999999999</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>51</v>
       </c>
@@ -975,7 +968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>52</v>
       </c>
@@ -983,7 +976,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>53</v>
       </c>
@@ -997,6 +990,25 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000360DE9767CDF0449BF75EAB371D3CB7" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="75cb9a07855af6ac97bd432464ca7c04">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784" xmlns:ns3="081a93ea-d517-42a5-a2b7-457060aa7471" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d1676634304aab9936f6a5a5f53c7423" ns2:_="" ns3:_="">
     <xsd:import namespace="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784"/>
@@ -1219,31 +1231,19 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B47A4D00-4721-442C-AD47-3B93A307A451}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B63010B1-DCFD-459D-9A94-0597FB3E1193}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="48eed89a-7418-4977-ae3a-838f0fac8ec5"/>
+    <ds:schemaRef ds:uri="416d42ac-85ec-40c4-8054-6c816fd4b6a7"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C1DBD38-A395-4168-A4DF-FA517531E2BE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5ADD9B66-4C76-449D-B320-D0F5D284B142}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
@@ -1251,5 +1251,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85C5F79F-8555-41A4-929B-AA5BAFCCACA5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31C3414B-5219-4D26-B2A4-3138B83D43E0}"/>
 </file>